--- a/骰宝数学-SicBo计算模型.xlsx
+++ b/骰宝数学-SicBo计算模型.xlsx
@@ -1701,6 +1701,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AI52" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3668,5 +3671,8 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:W70" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/骰宝数学-SicBo计算模型.xlsx
+++ b/骰宝数学-SicBo计算模型.xlsx
@@ -10,7 +10,7 @@
     <sheet name="说明" sheetId="1" r:id="rId1"/>
     <sheet name="SicBo 递推表+下注RTP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -951,7 +951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -967,6 +967,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1358,318 +1361,318 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:11">
-      <c r="A2" s="13"/>
+      <c r="A2" s="16"/>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:11">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:11">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:11">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:11">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:11">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:11">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:11">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:11">
-      <c r="A10" s="13"/>
+      <c r="A10" s="16"/>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:11">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:11">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:11">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:11">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:11">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:11">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:30">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:30">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:30">
-      <c r="A19" s="13"/>
+      <c r="A19" s="16"/>
     </row>
     <row r="20" ht="45" customHeight="1" spans="1:30">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:30">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:30">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:30">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:30">
-      <c r="A24" s="13"/>
+      <c r="A24" s="16"/>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:30">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:30">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:30">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:30">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:30">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:30">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:30">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:30">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="24">
